--- a/daily_matches/job_matches_2026-07-30.xlsx
+++ b/daily_matches/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Platform Engineer I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4013000b557f3707</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Harness Engineers</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, S3, Kubernetes, CI/CD, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c0976212ce983e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist, Forecasting and Analytics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,137 +566,137 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5cfa2b4e92424b</t>
+          <t>https://www.indeed.com/viewjob?jk=125376be857aeaac</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Prompt Engineer</t>
+          <t>Sr Engineer, Machine Learning Engineering (ML Apps)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, AKS, CI/CD, Git, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c2fcf67148e57f</t>
+          <t>https://www.indeed.com/viewjob?jk=147dd0427dc3d860</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Spring)</t>
+          <t>Software Developer/Engineer (Mid Level experience)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, Docker, Kubernetes, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f9c7c087570b67</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Information and Referral Federation of Los Angeles County</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Kinesis, CI/CD, Git, Redshift, Tableau, Python, SQL</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
+          <t>https://www.indeed.com/viewjob?jk=3b71e8980fb3c592</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (US Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, S3, Python, R, Scala</t>
+          <t>CI/CD, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,287 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b633ad954bf00888</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Financial Engineering</t>
+          <t>Senior GPU Performance and Power Benchmark Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk Analytics</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Guilford, CT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, PyTorch, Docker, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sr. Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sr. Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr. Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Developer/Engineer (Mid Level experience)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Tech Army</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, Docker, Kubernetes, Python, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c123253362f4f97f</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>University of Utah</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, Gemini, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aca0ab75425d2229</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer - Content Platform</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Expedia Group</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Cassandra, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5fac42e3eb05e313</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Applied AI ML - Senior Associate</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87d0c10e26051819</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd100e445d40723</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-30.xlsx
+++ b/daily_matches/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Platform Engineer I</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>ClassWallet</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4013000b557f3707</t>
+          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
+          <t>Senior Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
+          <t>https://www.indeed.com/viewjob?jk=34fdb7f22611e005</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Forecasting and Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125376be857aeaac</t>
+          <t>https://www.indeed.com/viewjob?jk=c137c0ee6e643b46</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Engineer, Machine Learning Engineering (ML Apps)</t>
+          <t>Early Career: IT Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147dd0427dc3d860</t>
+          <t>https://www.indeed.com/viewjob?jk=536a5cbcba65868f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer/Engineer (Mid Level experience)</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, Docker, Kubernetes, Python, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f9c7c087570b67</t>
+          <t>https://www.indeed.com/viewjob?jk=77a96e5bb975df12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b71e8980fb3c592</t>
+          <t>https://www.indeed.com/viewjob?jk=2414ca1640b2e6d9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI &amp; Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,52 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CI/CD, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior GPU Performance and Power Benchmark Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, Docker, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd100e445d40723</t>
+          <t>https://www.indeed.com/viewjob?jk=625253be1b67957f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-30.xlsx
+++ b/daily_matches/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ClassWallet</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, NoSQL, Python</t>
+          <t>Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34fdb7f22611e005</t>
+          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer Sr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c137c0ee6e643b46</t>
+          <t>https://www.indeed.com/viewjob?jk=afd5e6e6ba9e3201</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Early Career: IT Security Engineer</t>
+          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, BigQuery, Kinesis, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=536a5cbcba65868f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a96e5bb975df12</t>
+          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Cloud Engineer Senior</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, S3, Athena, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,427 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2414ca1640b2e6d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist</t>
+          <t>Senior Engineer, Data and AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>Cisive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, MLflow, FastAPI, Databricks, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Fraud</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, Snowflake, BigQuery</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cd8962bf35fa6a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Data Lake, FastAPI, CI/CD, Git, Snowflake, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Salesforce Development Engineer II</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Terraform, Git, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Analytics Engineer II (Epic Cogito, Power BI)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Children's Health</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b2076122b255218</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ultralytics LLC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=625253be1b67957f</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PyTorch, OpenCV, YOLO, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cf04ffef915bc29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI/ML Platform Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>American Red Cross</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, Redshift, Terraform, Git, Databricks, Redshift, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2f29bd26a0640a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Software Engineer- Medicare Billing &amp; Care Management Platforms</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Symphony Solutions</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Athena, CI/CD, Git, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4b4ee1a15a9b71f</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Software Engineer- Medicare Billing &amp; Care Management Platforms</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Symphony Solutions</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Athena, CI/CD, Git, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63650eef78222599</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1031867682cdaf9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SmartRent</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, MLflow, Snowflake, Databricks, PySpark, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d559f9df787941e9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-30.xlsx
+++ b/daily_matches/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD</t>
+          <t>RAG, Cortex, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Hadoop, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
+          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Senior AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, MLflow, CI/CD, Git, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
+          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer Sr</t>
+          <t>Sr Data Analyst, Healthcare Claims Audit and Compliance (Hybrid NY)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Healthfirst</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>RAG, Glue, Redshift, Kinesis, Redshift, Hadoop, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd5e6e6ba9e3201</t>
+          <t>https://www.indeed.com/viewjob?jk=e9062a4d6025a698</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
+          <t>Full-Stack Software Engineer, Platform Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Zanskar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, Terraform, Snowflake, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a744de7685bedc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer Senior</t>
+          <t>AI Co Pilot Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Antra, Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Athena, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
+          <t>https://www.indeed.com/viewjob?jk=be8bbb18a774fab7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data and AI</t>
+          <t>Systems Security Engineer I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cisive</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, MLflow, FastAPI, Databricks, NoSQL, Python, SQL, R</t>
+          <t>RAG, AKS, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
+          <t>https://www.indeed.com/viewjob?jk=b478c60c75d45c2c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Fraud</t>
+          <t>Sr. Optimizely Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, Snowflake, BigQuery</t>
+          <t>RAG, Copilot, S3, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,357 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd8962bf35fa6a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GM Financial</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Cardiff</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Athena, Data Lake, FastAPI, CI/CD, Git, Snowflake, Python</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Salesforce Development Engineer II</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GM Financial</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Arlington, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Terraform, Git, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Analytics Engineer II (Epic Cogito, Power BI)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Children's Health</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2076122b255218</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ultralytics LLC</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>PyTorch, OpenCV, YOLO, Docker, Kubernetes, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf04ffef915bc29</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI/ML Platform Operations Analyst</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>American Red Cross</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, S3, Redshift, Terraform, Git, Databricks, Redshift, Python, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f29bd26a0640a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI Software Engineer- Medicare Billing &amp; Care Management Platforms</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Symphony Solutions</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Athena, CI/CD, Git, MySQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b4ee1a15a9b71f</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AI Software Engineer- Medicare Billing &amp; Care Management Platforms</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Symphony Solutions</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Athena, CI/CD, Git, MySQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63650eef78222599</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1031867682cdaf9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SmartRent</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, MLflow, Snowflake, Databricks, PySpark, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d559f9df787941e9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8a1eee5afb1175</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-30.xlsx
+++ b/daily_matches/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Data Engineer - Onboarding</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Cortex, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Hadoop, NoSQL, Python</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, CatBoost, BigQuery, Dataflow, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
+          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI/ML Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, MLflow, CI/CD, Git, BigQuery, Python, SQL</t>
+          <t>AI Engineer, RAG, S3, Athena, Redshift, BigQuery, Data Lake, Kinesis, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Analyst, Healthcare Claims Audit and Compliance (Hybrid NY)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Healthfirst</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, Kinesis, Redshift, Hadoop, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9062a4d6025a698</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer, Platform Data</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zanskar</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, Terraform, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a744de7685bedc</t>
+          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Python-AI_ML-GenAI- Senior Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
+          <t>https://www.indeed.com/viewjob?jk=0c55d5a480e1ba95</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Co Pilot Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Antra, Inc</t>
+          <t>Arm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be8bbb18a774fab7</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ab87ab6ebb7645</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Systems Security Engineer I</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Dutch Bros Coffee</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, AKS, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, Snowflake, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,1337 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b478c60c75d45c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd616fb4621cbc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Optimizely Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>Balt Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Cortex, Data Lake, Git, Snowflake, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d78010c69b758f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Cloud DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Michael Baker International</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Copy of Consultant – Compliance Data Science &amp; AI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SIA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Git, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e059ab1a71254bff</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Consultant – Compliance Data Science &amp; AI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SIA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Git, Python</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87c77f182c9612cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Consultant – Compliance Data Science &amp; AI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SIA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Git, Python</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14a27ac651b85ab3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI Product Software Engineer (Laravel / Vue)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Stanbridge University</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aaba8374f9a21b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer - ML Infrastructure</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Epsilon Labs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, BigQuery, Docker, Kubernetes, Snowflake, Databricks, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior CloudOps Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Domo, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer (AI-Powered EdTech)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Colleague AI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Kirkland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f442a707cd3f7bfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Engineer — GTM Analytics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57b4b8208d73f6c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer - Senior</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>London, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=deb8b30a116c1f6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Solutions Designer, Automation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Highlands Ranch, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Kubernetes, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56c50f1ddf149cd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Underwriting</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FloatMe</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Copilot, PyTorch, XGBoost, LightGBM, Git, Snowflake, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1be5247f8456284</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Data Mining</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a06b9d59efa5188d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Data Mining</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dff0b6bbf207038</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Data Mining</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=258829dc2e9acc12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Consultant- Marketing Data Science &amp; AI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SIA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, LLaMA, Gemini, Mistral, Hugging Face, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4de02abd02ee5722</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Consultant- Marketing Data Science &amp; AI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SIA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, LLaMA, Gemini, Mistral, Hugging Face, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92c4bbcc9502e775</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Consultant- Marketing Data Science &amp; AI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SIA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, LLaMA, Gemini, Mistral, Hugging Face, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=305039a0993d65ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Intern - Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Optimum</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Long Island City, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=081eaac72f9b8ed3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Grainger</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20688d3571cc1af7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Epsilon Labs</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6afbb65fc2479492</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Engineer - Emergency Preparedness and Response</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DTE Energy</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Databricks, Power BI, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9113d48eef000e71</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Engineer - AI Security</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Exelixis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Alameda, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8a1eee5afb1175</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f2519fa9db6a487</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Customer Engineer, Data &amp; Analytics Req#112</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Premier Cloud</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Git, BigQuery, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62cda4b6604958cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hightower Advisors</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, Snowflake, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Roseville, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c22a11a214d08e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5831d26c5aea0047</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91e4932d96dc49f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>National Interstate</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Richfield, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bc9f7daf1dd2d86</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Software Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>National Interstate</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8f6b67099175c94</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Finance AI Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Intuitive (Intuitive Surgical)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Prompt Engineering, Cortex, Snowflake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db78b1c632c52bdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Consulting Data Architect</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>World Wide Technology</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Git, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Private Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff5e986a6e270020</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Java-Python-Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Objectways Technologies</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6024f53ddc28e733</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Analyst, Applied AI Solutions</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7819ac55bf7b0b1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CCaaS-Five9-GCP-Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Objectways Technologies</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0dadf674013a062</t>
         </is>
       </c>
     </row>
